--- a/Assets/Resource/Magic/New/Magic.xlsx
+++ b/Assets/Resource/Magic/New/Magic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Unity_Card\Unity_Card\Assets\Resource\Magic\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773A3229-19F7-4167-86D0-9EE426FD5EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABBE15A-352A-4079-9400-8EFCCE855EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
   <si>
     <t>剑刺</t>
   </si>
@@ -63,358 +63,364 @@
     <t>潮汐</t>
   </si>
   <si>
+    <t>瀑流</t>
+  </si>
+  <si>
+    <t>进攻时，草法术额外附带摸一张牌</t>
+  </si>
+  <si>
+    <t>水刃</t>
+  </si>
+  <si>
+    <t>进攻时，物理攻击额外附带摸一张牌</t>
+  </si>
+  <si>
+    <t>冰封铠甲</t>
+  </si>
+  <si>
+    <t>物理防御的抵挡值翻倍（但即使伤害只有一点，也需要消耗一张牌）</t>
+  </si>
+  <si>
+    <t>沼泽</t>
+  </si>
+  <si>
+    <t>水墙</t>
+  </si>
+  <si>
+    <t>水法术可以防御一次任意点的任意类型伤害</t>
+  </si>
+  <si>
+    <t>蒸汽锅炉</t>
+  </si>
+  <si>
+    <t>爆燃</t>
+  </si>
+  <si>
+    <t>进攻时，火法术额外附带一点火元素伤害</t>
+  </si>
+  <si>
+    <t>淬火</t>
+  </si>
+  <si>
+    <t>进攻时，物理攻击额外附带一点火元素伤害</t>
+  </si>
+  <si>
+    <t>火雨</t>
+  </si>
+  <si>
+    <t>使用火法术防御之后，本回合免疫草元素伤害</t>
+  </si>
+  <si>
+    <t>熔岩之甲</t>
+  </si>
+  <si>
+    <t>火法术和火系技能可以转化为圆盾使用</t>
+  </si>
+  <si>
+    <t>熔炉</t>
+  </si>
+  <si>
+    <t>你可以将任意两张牌转化为一个圆盾</t>
+  </si>
+  <si>
+    <t>蒸腾</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
+  </si>
+  <si>
+    <t>进攻时，草法术可以转化剑刺，物理攻击可以转化为火法术</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（0消耗，摸一张牌）</t>
+  </si>
+  <si>
+    <t>木盾</t>
+  </si>
+  <si>
+    <t>防御时可以将该技能翻面，视为你使用了一个圆盾。轮到你进攻时，此技能恢复正面</t>
+  </si>
+  <si>
+    <t>进化</t>
+  </si>
+  <si>
+    <t>受到攻击使你的死亡感应触发时，你摸一张牌</t>
+  </si>
+  <si>
+    <t>毒刺</t>
+  </si>
+  <si>
+    <t>当你使用草法术防御时，对方损失一点法力</t>
+  </si>
+  <si>
+    <t>光芒</t>
+  </si>
+  <si>
+    <t>恢复一点法力，抽一张牌</t>
+  </si>
+  <si>
+    <t>凝露</t>
+  </si>
+  <si>
+    <t>辉光</t>
+  </si>
+  <si>
+    <t>恢复满法力值</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>图腾</t>
+  </si>
+  <si>
+    <t>结晶</t>
+  </si>
+  <si>
+    <t>透镜</t>
+  </si>
+  <si>
+    <t>法力牌额外恢复一点法力值</t>
+  </si>
+  <si>
+    <t>满月</t>
+  </si>
+  <si>
+    <t>当法力值大于等于2时，对于法术伤害，可以减少一点法力值，抵挡一点伤害</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>每使用一张物理攻击，恢复一点法力</t>
+  </si>
+  <si>
+    <t>龟甲</t>
+  </si>
+  <si>
+    <t>使用元素法术防御时不消耗法力</t>
+  </si>
+  <si>
+    <t>启示</t>
+  </si>
+  <si>
+    <t>所有法术不再消耗法力，但无法再打出法力牌。因其它技能所导致的额外法力消耗不会减免</t>
+  </si>
+  <si>
+    <t>驱散</t>
+  </si>
+  <si>
+    <t>移除对方的1个技能</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>展示你的一张手牌，然后将模仿当做这张手牌立即使用。不可以模仿技能</t>
+  </si>
+  <si>
+    <t>坟场</t>
+  </si>
+  <si>
+    <t>获得对方刚使用完毕或者弃掉的一张手牌，不可以获得技能</t>
+  </si>
+  <si>
+    <t>巫术响指</t>
+  </si>
+  <si>
+    <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
+  </si>
+  <si>
+    <t>城墙术</t>
+  </si>
+  <si>
+    <t>将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
+  </si>
+  <si>
+    <t>风暴</t>
+  </si>
+  <si>
+    <t>扭曲空间</t>
+  </si>
+  <si>
+    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
+  </si>
+  <si>
+    <t>杀戮本能</t>
+  </si>
+  <si>
+    <t>当你的攻击触发对方的死亡感应后，你摸一张牌</t>
+  </si>
+  <si>
+    <t>铸剑</t>
+  </si>
+  <si>
+    <t>进攻开始时，从弃牌堆当中获得一张剑刺（若有）</t>
+  </si>
+  <si>
+    <t>魔典</t>
+  </si>
+  <si>
+    <t>可以将物理攻击牌转化为特殊法术机遇（0消耗，摸一张牌）</t>
+  </si>
+  <si>
+    <t>权杖</t>
+  </si>
+  <si>
+    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
+  </si>
+  <si>
+    <t>恢复两点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kindDescription</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timingForPutting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Property</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理防御</t>
+  </si>
+  <si>
+    <t>物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击/物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>进攻时，水法术额外附带摸一张牌</t>
-  </si>
-  <si>
-    <t>瀑流</t>
-  </si>
-  <si>
-    <t>进攻时，草法术额外附带摸一张牌</t>
-  </si>
-  <si>
-    <t>水刃</t>
-  </si>
-  <si>
-    <t>进攻时，物理攻击额外附带摸一张牌</t>
-  </si>
-  <si>
-    <t>冰封铠甲</t>
-  </si>
-  <si>
-    <t>物理防御的抵挡值翻倍（但即使伤害只有一点，也需要消耗一张牌）</t>
-  </si>
-  <si>
-    <t>沼泽</t>
-  </si>
-  <si>
-    <t>水墙</t>
-  </si>
-  <si>
-    <t>水法术可以防御一次任意点的任意类型伤害</t>
-  </si>
-  <si>
-    <t>蒸汽锅炉</t>
-  </si>
-  <si>
-    <t>爆燃</t>
-  </si>
-  <si>
-    <t>进攻时，火法术额外附带一点火元素伤害</t>
-  </si>
-  <si>
-    <t>淬火</t>
-  </si>
-  <si>
-    <t>进攻时，物理攻击额外附带一点火元素伤害</t>
-  </si>
-  <si>
-    <t>火雨</t>
-  </si>
-  <si>
-    <t>使用火法术防御之后，本回合免疫草元素伤害</t>
-  </si>
-  <si>
-    <t>熔岩之甲</t>
-  </si>
-  <si>
-    <t>火法术和火系技能可以转化为圆盾使用</t>
-  </si>
-  <si>
-    <t>熔炉</t>
-  </si>
-  <si>
-    <t>你可以将任意两张牌转化为一个圆盾</t>
-  </si>
-  <si>
-    <t>蒸腾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>声明一种元素类型，风暴将变成该类型的元素法术。造成等同于当前法力值的伤害，并且消耗所有法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>进攻时，草法术可以转化剑刺，物理攻击可以转化为火法术</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（0消耗，摸一张牌）</t>
-  </si>
-  <si>
-    <t>木盾</t>
-  </si>
-  <si>
-    <t>防御时可以将该技能翻面，视为你使用了一个圆盾。轮到你进攻时，此技能恢复正面</t>
-  </si>
-  <si>
-    <t>进化</t>
-  </si>
-  <si>
-    <t>受到攻击使你的死亡感应触发时，你摸一张牌</t>
-  </si>
-  <si>
-    <t>毒刺</t>
-  </si>
-  <si>
-    <t>当你使用草法术防御时，对方损失一点法力</t>
-  </si>
-  <si>
-    <t>光芒</t>
-  </si>
-  <si>
-    <t>恢复一点法力，抽一张牌</t>
-  </si>
-  <si>
-    <t>凝露</t>
-  </si>
-  <si>
-    <t>辉光</t>
-  </si>
-  <si>
-    <t>恢复满法力值</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>进攻开始时恢复一点法力值</t>
-  </si>
-  <si>
-    <t>图腾</t>
-  </si>
-  <si>
-    <t>将一张法术牌转化为法力牌微光（恢复一点法力）</t>
-  </si>
-  <si>
-    <t>结晶</t>
-  </si>
-  <si>
-    <t>增加三点法力上限</t>
-  </si>
-  <si>
-    <t>透镜</t>
-  </si>
-  <si>
-    <t>法力牌额外恢复一点法力值</t>
-  </si>
-  <si>
-    <t>满月</t>
-  </si>
-  <si>
-    <t>当法力值大于等于2时，对于法术伤害，可以减少一点法力值，抵挡一点伤害</t>
-  </si>
-  <si>
-    <t>电弧</t>
-  </si>
-  <si>
-    <t>每使用一张物理攻击，恢复一点法力</t>
-  </si>
-  <si>
-    <t>龟甲</t>
-  </si>
-  <si>
-    <t>使用元素法术防御时不消耗法力</t>
-  </si>
-  <si>
-    <t>启示</t>
-  </si>
-  <si>
-    <t>所有法术不再消耗法力，但无法再打出法力牌。因其它技能所导致的额外法力消耗不会减免</t>
-  </si>
-  <si>
-    <t>驱散</t>
-  </si>
-  <si>
-    <t>移除对方的1个技能</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>展示你的一张手牌，然后将模仿当做这张手牌立即使用。不可以模仿技能</t>
-  </si>
-  <si>
-    <t>坟场</t>
-  </si>
-  <si>
-    <t>获得对方刚使用完毕或者弃掉的一张手牌，不可以获得技能</t>
-  </si>
-  <si>
-    <t>巫术响指</t>
-  </si>
-  <si>
-    <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
-  </si>
-  <si>
-    <t>城墙术</t>
-  </si>
-  <si>
-    <t>将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
-  </si>
-  <si>
-    <t>风暴</t>
-  </si>
-  <si>
-    <t>移除掉你的任意个技能，每移除一个摸一张牌，并且恢复一点法力值</t>
-  </si>
-  <si>
-    <t>扭曲空间</t>
-  </si>
-  <si>
-    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
-  </si>
-  <si>
-    <t>杀戮本能</t>
-  </si>
-  <si>
-    <t>当你的攻击触发对方的死亡感应后，你摸一张牌</t>
-  </si>
-  <si>
-    <t>铸剑</t>
-  </si>
-  <si>
-    <t>进攻开始时，从弃牌堆当中获得一张剑刺（若有）</t>
-  </si>
-  <si>
-    <t>魔典</t>
-  </si>
-  <si>
-    <t>可以将物理攻击牌转化为特殊法术机遇（0消耗，摸一张牌）</t>
-  </si>
-  <si>
-    <t>权杖</t>
-  </si>
-  <si>
-    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
-  </si>
-  <si>
-    <t>恢复两点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kindDescription</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isSkill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>timingForPutting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Property</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effectCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理防御</t>
-  </si>
-  <si>
-    <t>物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击/物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点火元素伤害；防御时抵挡一点物理/草元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点草元素伤害；防御时抵挡一点物理/水元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点水元素伤害；防御时抵挡一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以将一张法术牌转化为法力牌微光（恢复一点法力）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加三点法力上限（不增加法力值）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点水元素伤害防御时抵挡一点火元素伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -794,7 +800,7 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="91.5546875" customWidth="1"/>
+    <col min="2" max="2" width="95.88671875" customWidth="1"/>
     <col min="6" max="6" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -815,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G1">
         <v>2</v>
@@ -844,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -873,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -902,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -919,7 +925,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -931,7 +937,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -945,10 +951,10 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -960,7 +966,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -974,10 +980,10 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -989,7 +995,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1003,10 +1009,10 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1018,7 +1024,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1030,12 +1036,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15">
+    <row r="9" spans="1:9" ht="15.6">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
+      <c r="B9" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1047,7 +1053,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1061,11 +1067,11 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
       <c r="C10">
         <v>0</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1090,11 +1096,11 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
       <c r="C11">
         <v>0</v>
       </c>
@@ -1105,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1119,11 +1125,11 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
       <c r="C12">
         <v>1</v>
       </c>
@@ -1134,7 +1140,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1148,10 +1154,10 @@
     </row>
     <row r="13" spans="1:9" ht="15.6">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1163,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1177,11 +1183,11 @@
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
       <c r="C14">
         <v>1</v>
       </c>
@@ -1192,7 +1198,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1206,10 +1212,10 @@
     </row>
     <row r="15" spans="1:9" ht="15.6">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1221,7 +1227,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1235,10 +1241,10 @@
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
         <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1250,7 +1256,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1264,10 +1270,10 @@
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
         <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1279,7 +1285,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1293,10 +1299,10 @@
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
         <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1308,7 +1314,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1322,10 +1328,10 @@
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
         <v>27</v>
-      </c>
-      <c r="B19" t="s">
-        <v>28</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1337,7 +1343,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1351,10 +1357,10 @@
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
         <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>30</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1366,7 +1372,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1378,12 +1384,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15">
+    <row r="21" spans="1:9" ht="15.6">
       <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1395,7 +1401,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1409,10 +1415,10 @@
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1424,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1438,10 +1444,10 @@
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1453,7 +1459,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1467,10 +1473,10 @@
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1482,7 +1488,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1496,10 +1502,10 @@
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -1511,7 +1517,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1525,10 +1531,10 @@
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1540,7 +1546,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1554,10 +1560,10 @@
     </row>
     <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1569,7 +1575,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1583,10 +1589,10 @@
     </row>
     <row r="28" spans="1:9" ht="15.6">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1598,7 +1604,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1612,10 +1618,10 @@
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1627,7 +1633,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1639,12 +1645,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15">
+    <row r="30" spans="1:9" ht="15.6">
       <c r="A30" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1656,7 +1662,7 @@
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1668,12 +1674,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15">
+    <row r="31" spans="1:9" ht="15.6">
       <c r="A31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1685,7 +1691,7 @@
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1697,12 +1703,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15">
+    <row r="32" spans="1:9" ht="15.6">
       <c r="A32" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1714,7 +1720,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1728,10 +1734,10 @@
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1743,7 +1749,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1757,10 +1763,10 @@
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1772,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1786,10 +1792,10 @@
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1801,7 +1807,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1815,10 +1821,10 @@
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1830,7 +1836,7 @@
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -1844,10 +1850,10 @@
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1859,7 +1865,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1873,10 +1879,10 @@
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1888,7 +1894,7 @@
         <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -1902,10 +1908,10 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1917,7 +1923,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -1926,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1946,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -1960,10 +1966,10 @@
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1975,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -1989,10 +1995,10 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2004,7 +2010,7 @@
         <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2016,12 +2022,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15">
+    <row r="43" spans="1:9" ht="15.6">
       <c r="A43" t="s">
-        <v>74</v>
-      </c>
-      <c r="B43" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2033,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2041,16 +2047,16 @@
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2062,7 +2068,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2076,10 +2082,10 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2091,7 +2097,7 @@
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2105,10 +2111,10 @@
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B46" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2120,7 +2126,7 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2129,15 +2135,15 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -2149,7 +2155,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2158,15 +2164,15 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -2178,7 +2184,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2192,25 +2198,25 @@
     </row>
     <row r="51" spans="3:9">
       <c r="C51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/New/Magic.xlsx
+++ b/Assets/Resource/Magic/New/Magic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Unity_Card\Unity_Card\Assets\Resource\Magic\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABBE15A-352A-4079-9400-8EFCCE855EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4939101F-2553-40CB-9DF5-7E54D537065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,361 +66,369 @@
     <t>瀑流</t>
   </si>
   <si>
+    <t>水刃</t>
+  </si>
+  <si>
+    <t>进攻时，物理攻击额外附带摸一张牌</t>
+  </si>
+  <si>
+    <t>冰封铠甲</t>
+  </si>
+  <si>
+    <t>物理防御的抵挡值翻倍（但即使伤害只有一点，也需要消耗一张牌）</t>
+  </si>
+  <si>
+    <t>沼泽</t>
+  </si>
+  <si>
+    <t>水墙</t>
+  </si>
+  <si>
+    <t>水法术可以防御一次任意点的任意类型伤害</t>
+  </si>
+  <si>
+    <t>蒸汽锅炉</t>
+  </si>
+  <si>
+    <t>爆燃</t>
+  </si>
+  <si>
+    <t>进攻时，火法术额外附带一点火元素伤害</t>
+  </si>
+  <si>
+    <t>淬火</t>
+  </si>
+  <si>
+    <t>进攻时，物理攻击额外附带一点火元素伤害</t>
+  </si>
+  <si>
+    <t>火雨</t>
+  </si>
+  <si>
+    <t>使用火法术防御之后，本回合免疫草元素伤害</t>
+  </si>
+  <si>
+    <t>熔岩之甲</t>
+  </si>
+  <si>
+    <t>蒸腾</t>
+  </si>
+  <si>
+    <t>进攻时，草法术可以转化剑刺，物理攻击可以转化为火法术</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（0消耗，摸一张牌）</t>
+  </si>
+  <si>
+    <t>木盾</t>
+  </si>
+  <si>
+    <t>防御时可以将该技能翻面，视为你使用了一个圆盾。轮到你进攻时，此技能恢复正面</t>
+  </si>
+  <si>
+    <t>进化</t>
+  </si>
+  <si>
+    <t>受到攻击使你的死亡感应触发时，你摸一张牌</t>
+  </si>
+  <si>
+    <t>光芒</t>
+  </si>
+  <si>
+    <t>凝露</t>
+  </si>
+  <si>
+    <t>辉光</t>
+  </si>
+  <si>
+    <t>恢复满法力值</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>图腾</t>
+  </si>
+  <si>
+    <t>结晶</t>
+  </si>
+  <si>
+    <t>透镜</t>
+  </si>
+  <si>
+    <t>法力牌额外恢复一点法力值</t>
+  </si>
+  <si>
+    <t>满月</t>
+  </si>
+  <si>
+    <t>当法力值大于等于2时，对于法术伤害，可以减少一点法力值，抵挡一点伤害</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>每使用一张物理攻击，恢复一点法力</t>
+  </si>
+  <si>
+    <t>龟甲</t>
+  </si>
+  <si>
+    <t>使用元素法术防御时不消耗法力</t>
+  </si>
+  <si>
+    <t>启示</t>
+  </si>
+  <si>
+    <t>所有法术不再消耗法力，但无法再打出法力牌。因其它技能所导致的额外法力消耗不会减免</t>
+  </si>
+  <si>
+    <t>驱散</t>
+  </si>
+  <si>
+    <t>移除对方的1个技能</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>展示你的一张手牌，然后将模仿当做这张手牌立即使用。不可以模仿技能</t>
+  </si>
+  <si>
+    <t>坟场</t>
+  </si>
+  <si>
+    <t>获得对方刚使用完毕或者弃掉的一张手牌，不可以获得技能</t>
+  </si>
+  <si>
+    <t>巫术响指</t>
+  </si>
+  <si>
+    <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
+  </si>
+  <si>
+    <t>城墙术</t>
+  </si>
+  <si>
+    <t>将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
+  </si>
+  <si>
+    <t>风暴</t>
+  </si>
+  <si>
+    <t>扭曲空间</t>
+  </si>
+  <si>
+    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
+  </si>
+  <si>
+    <t>杀戮本能</t>
+  </si>
+  <si>
+    <t>当你的攻击触发对方的死亡感应后，你摸一张牌</t>
+  </si>
+  <si>
+    <t>铸剑</t>
+  </si>
+  <si>
+    <t>进攻开始时，从弃牌堆当中获得一张剑刺（若有）</t>
+  </si>
+  <si>
+    <t>魔典</t>
+  </si>
+  <si>
+    <t>可以将物理攻击牌转化为特殊法术机遇（0消耗，摸一张牌）</t>
+  </si>
+  <si>
+    <t>权杖</t>
+  </si>
+  <si>
+    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
+  </si>
+  <si>
+    <t>恢复两点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kindDescription</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timingForPutting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Property</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理防御</t>
+  </si>
+  <si>
+    <t>物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击/物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>声明一种元素类型，风暴将变成该类型的元素法术。造成等同于当前法力值的伤害，并且消耗所有法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻开始时恢复一点法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以将一张法术牌转化为法力牌微光（恢复一点法力）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加三点法力上限（不增加法力值）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点水元素伤害\n防御时抵挡一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>进攻时，草法术额外附带摸一张牌</t>
-  </si>
-  <si>
-    <t>水刃</t>
-  </si>
-  <si>
-    <t>进攻时，物理攻击额外附带摸一张牌</t>
-  </si>
-  <si>
-    <t>冰封铠甲</t>
-  </si>
-  <si>
-    <t>物理防御的抵挡值翻倍（但即使伤害只有一点，也需要消耗一张牌）</t>
-  </si>
-  <si>
-    <t>沼泽</t>
-  </si>
-  <si>
-    <t>水墙</t>
-  </si>
-  <si>
-    <t>水法术可以防御一次任意点的任意类型伤害</t>
-  </si>
-  <si>
-    <t>蒸汽锅炉</t>
-  </si>
-  <si>
-    <t>爆燃</t>
-  </si>
-  <si>
-    <t>进攻时，火法术额外附带一点火元素伤害</t>
-  </si>
-  <si>
-    <t>淬火</t>
-  </si>
-  <si>
-    <t>进攻时，物理攻击额外附带一点火元素伤害</t>
-  </si>
-  <si>
-    <t>火雨</t>
-  </si>
-  <si>
-    <t>使用火法术防御之后，本回合免疫草元素伤害</t>
-  </si>
-  <si>
-    <t>熔岩之甲</t>
-  </si>
-  <si>
-    <t>火法术和火系技能可以转化为圆盾使用</t>
-  </si>
-  <si>
-    <t>熔炉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复一点法力，摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烧伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你使用火法术防御时，对方损失一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>你可以将任意两张牌转化为一个圆盾</t>
-  </si>
-  <si>
-    <t>蒸腾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术和草系技能可以转化为圆盾使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>藤蔓</t>
-  </si>
-  <si>
-    <t>进攻时，草法术可以转化剑刺，物理攻击可以转化为火法术</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（0消耗，摸一张牌）</t>
-  </si>
-  <si>
-    <t>木盾</t>
-  </si>
-  <si>
-    <t>防御时可以将该技能翻面，视为你使用了一个圆盾。轮到你进攻时，此技能恢复正面</t>
-  </si>
-  <si>
-    <t>进化</t>
-  </si>
-  <si>
-    <t>受到攻击使你的死亡感应触发时，你摸一张牌</t>
-  </si>
-  <si>
-    <t>毒刺</t>
-  </si>
-  <si>
-    <t>当你使用草法术防御时，对方损失一点法力</t>
-  </si>
-  <si>
-    <t>光芒</t>
-  </si>
-  <si>
-    <t>恢复一点法力，抽一张牌</t>
-  </si>
-  <si>
-    <t>凝露</t>
-  </si>
-  <si>
-    <t>辉光</t>
-  </si>
-  <si>
-    <t>恢复满法力值</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>图腾</t>
-  </si>
-  <si>
-    <t>结晶</t>
-  </si>
-  <si>
-    <t>透镜</t>
-  </si>
-  <si>
-    <t>法力牌额外恢复一点法力值</t>
-  </si>
-  <si>
-    <t>满月</t>
-  </si>
-  <si>
-    <t>当法力值大于等于2时，对于法术伤害，可以减少一点法力值，抵挡一点伤害</t>
-  </si>
-  <si>
-    <t>电弧</t>
-  </si>
-  <si>
-    <t>每使用一张物理攻击，恢复一点法力</t>
-  </si>
-  <si>
-    <t>龟甲</t>
-  </si>
-  <si>
-    <t>使用元素法术防御时不消耗法力</t>
-  </si>
-  <si>
-    <t>启示</t>
-  </si>
-  <si>
-    <t>所有法术不再消耗法力，但无法再打出法力牌。因其它技能所导致的额外法力消耗不会减免</t>
-  </si>
-  <si>
-    <t>驱散</t>
-  </si>
-  <si>
-    <t>移除对方的1个技能</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>展示你的一张手牌，然后将模仿当做这张手牌立即使用。不可以模仿技能</t>
-  </si>
-  <si>
-    <t>坟场</t>
-  </si>
-  <si>
-    <t>获得对方刚使用完毕或者弃掉的一张手牌，不可以获得技能</t>
-  </si>
-  <si>
-    <t>巫术响指</t>
-  </si>
-  <si>
-    <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
-  </si>
-  <si>
-    <t>城墙术</t>
-  </si>
-  <si>
-    <t>将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
-  </si>
-  <si>
-    <t>风暴</t>
-  </si>
-  <si>
-    <t>扭曲空间</t>
-  </si>
-  <si>
-    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
-  </si>
-  <si>
-    <t>杀戮本能</t>
-  </si>
-  <si>
-    <t>当你的攻击触发对方的死亡感应后，你摸一张牌</t>
-  </si>
-  <si>
-    <t>铸剑</t>
-  </si>
-  <si>
-    <t>进攻开始时，从弃牌堆当中获得一张剑刺（若有）</t>
-  </si>
-  <si>
-    <t>魔典</t>
-  </si>
-  <si>
-    <t>可以将物理攻击牌转化为特殊法术机遇（0消耗，摸一张牌）</t>
-  </si>
-  <si>
-    <t>权杖</t>
-  </si>
-  <si>
-    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
-  </si>
-  <si>
-    <t>恢复两点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kindDescription</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isSkill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>timingForPutting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Property</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effectCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理防御</t>
-  </si>
-  <si>
-    <t>物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击/物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>声明一种元素类型，风暴将变成该类型的元素法术。造成等同于当前法力值的伤害，并且消耗所有法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻开始时恢复一点法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，可以将一张法术牌转化为法力牌微光（恢复一点法力）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加三点法力上限（不增加法力值）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点水元素伤害防御时抵挡一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荆棘</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -821,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G1">
         <v>2</v>
@@ -850,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -879,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -908,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -925,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -937,7 +945,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -951,10 +959,10 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -966,7 +974,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -980,10 +988,10 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -995,7 +1003,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1009,10 +1017,10 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1024,7 +1032,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1041,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1053,7 +1061,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1065,12 +1073,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15">
+    <row r="10" spans="1:9" ht="15.6">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
+      <c r="B10" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1082,7 +1090,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1096,11 +1104,11 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
       <c r="C11">
         <v>0</v>
       </c>
@@ -1111,7 +1119,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1125,11 +1133,11 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
       <c r="C12">
         <v>1</v>
       </c>
@@ -1140,7 +1148,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1154,10 +1162,10 @@
     </row>
     <row r="13" spans="1:9" ht="15.6">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1169,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1183,11 +1191,11 @@
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
       <c r="C14">
         <v>1</v>
       </c>
@@ -1198,7 +1206,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1212,10 +1220,10 @@
     </row>
     <row r="15" spans="1:9" ht="15.6">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1227,7 +1235,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1241,10 +1249,10 @@
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1256,7 +1264,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1270,10 +1278,10 @@
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
         <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1285,7 +1293,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1299,10 +1307,10 @@
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
         <v>24</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1314,7 +1322,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1326,12 +1334,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15">
+    <row r="19" spans="1:9" ht="15.6">
       <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1343,7 +1351,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1352,15 +1360,15 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.6">
+      <c r="A20" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1372,7 +1380,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1386,10 +1394,10 @@
     </row>
     <row r="21" spans="1:9" ht="15.6">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1401,7 +1409,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1413,12 +1421,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15">
-      <c r="A22" t="s">
-        <v>31</v>
+    <row r="22" spans="1:9" ht="15.6">
+      <c r="A22" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1430,7 +1438,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1444,10 +1452,10 @@
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1459,7 +1467,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1473,13 +1481,13 @@
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1488,7 +1496,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1497,18 +1505,18 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1517,7 +1525,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1529,12 +1537,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15">
-      <c r="A26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
+    <row r="26" spans="1:9" ht="15.6">
+      <c r="A26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1546,7 +1554,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1558,12 +1566,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15">
+    <row r="27" spans="1:9" ht="15.6">
       <c r="A27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" t="s">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1575,7 +1583,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1589,22 +1597,22 @@
     </row>
     <row r="28" spans="1:9" ht="15.6">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1618,10 +1626,10 @@
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1633,7 +1641,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1647,10 +1655,10 @@
     </row>
     <row r="30" spans="1:9" ht="15.6">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1662,7 +1670,7 @@
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1676,10 +1684,10 @@
     </row>
     <row r="31" spans="1:9" ht="15.6">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1691,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1705,10 +1713,10 @@
     </row>
     <row r="32" spans="1:9" ht="15.6">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1720,7 +1728,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1734,10 +1742,10 @@
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1749,7 +1757,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1763,10 +1771,10 @@
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1778,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1792,10 +1800,10 @@
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1807,7 +1815,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1821,10 +1829,10 @@
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1836,7 +1844,7 @@
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -1850,10 +1858,10 @@
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1865,7 +1873,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1879,10 +1887,10 @@
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1894,7 +1902,7 @@
         <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -1908,10 +1916,10 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1923,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -1932,15 +1940,15 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1952,7 +1960,7 @@
         <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -1966,10 +1974,10 @@
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B41" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1981,7 +1989,7 @@
         <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -1995,10 +2003,10 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2010,7 +2018,7 @@
         <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2024,10 +2032,10 @@
     </row>
     <row r="43" spans="1:9" ht="15.6">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2039,7 +2047,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2048,15 +2056,15 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2068,10 +2076,10 @@
         <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2082,10 +2090,10 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2097,10 +2105,10 @@
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2111,10 +2119,10 @@
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2126,10 +2134,10 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -2140,10 +2148,10 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -2155,10 +2163,10 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -2169,10 +2177,10 @@
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -2184,10 +2192,10 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2198,25 +2206,25 @@
     </row>
     <row r="51" spans="3:9">
       <c r="C51" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/New/Magic.xlsx
+++ b/Assets/Resource/Magic/New/Magic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Unity_Card\Unity_Card\Assets\Resource\Magic\New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity_Project\Unity_Card\Assets\Resource\Magic\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4939101F-2553-40CB-9DF5-7E54D537065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC7E052-3D73-4136-81FA-6083F67B7FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="122">
   <si>
     <t>剑刺</t>
   </si>
@@ -42,393 +42,415 @@
     <t>圆盾</t>
   </si>
   <si>
+    <t>一刀斩</t>
+  </si>
+  <si>
+    <t>造成一点物理伤害，当对方死亡感应触发时，额外造成一点物理伤害</t>
+  </si>
+  <si>
+    <t>星之盾</t>
+  </si>
+  <si>
+    <t>抵挡三点任意类型伤害</t>
+  </si>
+  <si>
+    <t>刺甲</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>瀑流</t>
+  </si>
+  <si>
+    <t>水刃</t>
+  </si>
+  <si>
+    <t>进攻时，物理攻击额外附带摸一张牌</t>
+  </si>
+  <si>
+    <t>冰封铠甲</t>
+  </si>
+  <si>
+    <t>物理防御的抵挡值翻倍（但即使伤害只有一点，也需要消耗一张牌）</t>
+  </si>
+  <si>
+    <t>沼泽</t>
+  </si>
+  <si>
+    <t>水墙</t>
+  </si>
+  <si>
+    <t>水法术可以防御一次任意点的任意类型伤害</t>
+  </si>
+  <si>
+    <t>蒸汽锅炉</t>
+  </si>
+  <si>
+    <t>爆燃</t>
+  </si>
+  <si>
+    <t>进攻时，火法术额外附带一点火元素伤害</t>
+  </si>
+  <si>
+    <t>淬火</t>
+  </si>
+  <si>
+    <t>进攻时，物理攻击额外附带一点火元素伤害</t>
+  </si>
+  <si>
+    <t>火雨</t>
+  </si>
+  <si>
+    <t>使用火法术防御之后，本回合免疫草元素伤害</t>
+  </si>
+  <si>
+    <t>熔岩之甲</t>
+  </si>
+  <si>
+    <t>蒸腾</t>
+  </si>
+  <si>
+    <t>进攻时，草法术可以转化剑刺，物理攻击可以转化为火法术</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（0消耗，摸一张牌）</t>
+  </si>
+  <si>
+    <t>木盾</t>
+  </si>
+  <si>
+    <t>防御时可以将该技能翻面，视为你使用了一个圆盾。轮到你进攻时，此技能恢复正面</t>
+  </si>
+  <si>
+    <t>进化</t>
+  </si>
+  <si>
+    <t>光芒</t>
+  </si>
+  <si>
+    <t>凝露</t>
+  </si>
+  <si>
+    <t>辉光</t>
+  </si>
+  <si>
+    <t>恢复满法力值</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>图腾</t>
+  </si>
+  <si>
+    <t>结晶</t>
+  </si>
+  <si>
+    <t>透镜</t>
+  </si>
+  <si>
+    <t>法力牌额外恢复一点法力值</t>
+  </si>
+  <si>
+    <t>满月</t>
+  </si>
+  <si>
+    <t>当法力值大于等于2时，对于法术伤害，可以减少一点法力值，抵挡一点伤害</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>每使用一张物理攻击，恢复一点法力</t>
+  </si>
+  <si>
+    <t>龟甲</t>
+  </si>
+  <si>
+    <t>使用元素法术防御时不消耗法力</t>
+  </si>
+  <si>
+    <t>启示</t>
+  </si>
+  <si>
+    <t>所有法术不再消耗法力，但无法再打出法力牌。因其它技能所导致的额外法力消耗不会减免</t>
+  </si>
+  <si>
+    <t>驱散</t>
+  </si>
+  <si>
+    <t>移除对方的1个技能</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>展示你的一张手牌，然后将模仿当做这张手牌立即使用。不可以模仿技能</t>
+  </si>
+  <si>
+    <t>坟场</t>
+  </si>
+  <si>
+    <t>获得对方刚使用完毕或者弃掉的一张手牌，不可以获得技能</t>
+  </si>
+  <si>
+    <t>巫术响指</t>
+  </si>
+  <si>
+    <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
+  </si>
+  <si>
+    <t>城墙术</t>
+  </si>
+  <si>
+    <t>风暴</t>
+  </si>
+  <si>
+    <t>扭曲空间</t>
+  </si>
+  <si>
+    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
+  </si>
+  <si>
+    <t>杀戮本能</t>
+  </si>
+  <si>
+    <t>铸剑</t>
+  </si>
+  <si>
+    <t>魔典</t>
+  </si>
+  <si>
+    <t>可以将物理攻击牌转化为特殊法术机遇（0消耗，摸一张牌）</t>
+  </si>
+  <si>
+    <t>权杖</t>
+  </si>
+  <si>
+    <t>恢复两点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kindDescription</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timingForPutting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Property</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理防御</t>
+  </si>
+  <si>
+    <t>物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击/物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻开始时恢复一点法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以将一张法术牌转化为法力牌微光（恢复一点法力）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点水元素伤害\n防御时抵挡一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，草法术额外附带摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复一点法力，摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烧伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你使用火法术防御时，对方损失一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以将任意两张牌转化为一个圆盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术和草系技能可以转化为圆盾使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤蔓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荆棘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加三点法力上限（不增加法力值），恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>抵挡一点任意类型伤害</t>
-  </si>
-  <si>
-    <t>一刀斩</t>
-  </si>
-  <si>
-    <t>造成一点物理伤害，当对方死亡感应触发时，额外造成一点物理伤害</t>
-  </si>
-  <si>
-    <t>星之盾</t>
-  </si>
-  <si>
-    <t>抵挡三点任意类型伤害</t>
-  </si>
-  <si>
-    <t>刺甲</t>
-  </si>
-  <si>
-    <t>潮汐</t>
-  </si>
-  <si>
-    <t>瀑流</t>
-  </si>
-  <si>
-    <t>水刃</t>
-  </si>
-  <si>
-    <t>进攻时，物理攻击额外附带摸一张牌</t>
-  </si>
-  <si>
-    <t>冰封铠甲</t>
-  </si>
-  <si>
-    <t>物理防御的抵挡值翻倍（但即使伤害只有一点，也需要消耗一张牌）</t>
-  </si>
-  <si>
-    <t>沼泽</t>
-  </si>
-  <si>
-    <t>水墙</t>
-  </si>
-  <si>
-    <t>水法术可以防御一次任意点的任意类型伤害</t>
-  </si>
-  <si>
-    <t>蒸汽锅炉</t>
-  </si>
-  <si>
-    <t>爆燃</t>
-  </si>
-  <si>
-    <t>进攻时，火法术额外附带一点火元素伤害</t>
-  </si>
-  <si>
-    <t>淬火</t>
-  </si>
-  <si>
-    <t>进攻时，物理攻击额外附带一点火元素伤害</t>
-  </si>
-  <si>
-    <t>火雨</t>
-  </si>
-  <si>
-    <t>使用火法术防御之后，本回合免疫草元素伤害</t>
-  </si>
-  <si>
-    <t>熔岩之甲</t>
-  </si>
-  <si>
-    <t>蒸腾</t>
-  </si>
-  <si>
-    <t>进攻时，草法术可以转化剑刺，物理攻击可以转化为火法术</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（0消耗，摸一张牌）</t>
-  </si>
-  <si>
-    <t>木盾</t>
-  </si>
-  <si>
-    <t>防御时可以将该技能翻面，视为你使用了一个圆盾。轮到你进攻时，此技能恢复正面</t>
-  </si>
-  <si>
-    <t>进化</t>
-  </si>
-  <si>
-    <t>受到攻击使你的死亡感应触发时，你摸一张牌</t>
-  </si>
-  <si>
-    <t>光芒</t>
-  </si>
-  <si>
-    <t>凝露</t>
-  </si>
-  <si>
-    <t>辉光</t>
-  </si>
-  <si>
-    <t>恢复满法力值</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>图腾</t>
-  </si>
-  <si>
-    <t>结晶</t>
-  </si>
-  <si>
-    <t>透镜</t>
-  </si>
-  <si>
-    <t>法力牌额外恢复一点法力值</t>
-  </si>
-  <si>
-    <t>满月</t>
-  </si>
-  <si>
-    <t>当法力值大于等于2时，对于法术伤害，可以减少一点法力值，抵挡一点伤害</t>
-  </si>
-  <si>
-    <t>电弧</t>
-  </si>
-  <si>
-    <t>每使用一张物理攻击，恢复一点法力</t>
-  </si>
-  <si>
-    <t>龟甲</t>
-  </si>
-  <si>
-    <t>使用元素法术防御时不消耗法力</t>
-  </si>
-  <si>
-    <t>启示</t>
-  </si>
-  <si>
-    <t>所有法术不再消耗法力，但无法再打出法力牌。因其它技能所导致的额外法力消耗不会减免</t>
-  </si>
-  <si>
-    <t>驱散</t>
-  </si>
-  <si>
-    <t>移除对方的1个技能</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>展示你的一张手牌，然后将模仿当做这张手牌立即使用。不可以模仿技能</t>
-  </si>
-  <si>
-    <t>坟场</t>
-  </si>
-  <si>
-    <t>获得对方刚使用完毕或者弃掉的一张手牌，不可以获得技能</t>
-  </si>
-  <si>
-    <t>巫术响指</t>
-  </si>
-  <si>
-    <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
-  </si>
-  <si>
-    <t>城墙术</t>
-  </si>
-  <si>
-    <t>将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
-  </si>
-  <si>
-    <t>风暴</t>
-  </si>
-  <si>
-    <t>扭曲空间</t>
-  </si>
-  <si>
-    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
-  </si>
-  <si>
-    <t>杀戮本能</t>
-  </si>
-  <si>
-    <t>当你的攻击触发对方的死亡感应后，你摸一张牌</t>
-  </si>
-  <si>
-    <t>铸剑</t>
-  </si>
-  <si>
-    <t>进攻开始时，从弃牌堆当中获得一张剑刺（若有）</t>
-  </si>
-  <si>
-    <t>魔典</t>
-  </si>
-  <si>
-    <t>可以将物理攻击牌转化为特殊法术机遇（0消耗，摸一张牌）</t>
-  </si>
-  <si>
-    <t>权杖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵挡一点任意类型伤害，可以将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一种元素，风暴转化为该元素法术。造成等同于当前法力值的伤害，并且消耗所有法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击使你的死亡感应触发时，你摸一张牌并且恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你的攻击触发对方的死亡感应后，你摸一张牌并且恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以消耗一法力，将你本回合使用的所有（非转化的）剑刺全部收回手中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
-  </si>
-  <si>
-    <t>恢复两点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kindDescription</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isSkill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>timingForPutting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Property</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effectCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理防御</t>
-  </si>
-  <si>
-    <t>物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击/物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>声明一种元素类型，风暴将变成该类型的元素法术。造成等同于当前法力值的伤害，并且消耗所有法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻开始时恢复一点法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，可以将一张法术牌转化为法力牌微光（恢复一点法力）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加三点法力上限（不增加法力值）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点水元素伤害\n防御时抵挡一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，草法术额外附带摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复一点法力，摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>烧伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你使用火法术防御时，对方损失一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你可以将任意两张牌转化为一个圆盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草法术和草系技能可以转化为圆盾使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藤蔓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>荆棘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用元素法术时，可以选择额外消耗两点法力，额外附带两点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺客护符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的物理攻击只能被 物理防御或者抵挡任意属性伤害的防御 挡住</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -829,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G1">
         <v>2</v>
@@ -841,12 +863,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15">
+    <row r="2" spans="1:9" ht="15.6">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -858,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -872,11 +894,11 @@
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
       <c r="C3">
         <v>2</v>
       </c>
@@ -887,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -901,11 +923,11 @@
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
       <c r="C4">
         <v>2</v>
       </c>
@@ -916,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -930,10 +952,10 @@
     </row>
     <row r="5" spans="1:9" ht="15.6">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -945,7 +967,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -959,10 +981,10 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -974,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -988,10 +1010,10 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1003,7 +1025,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1017,10 +1039,10 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1032,7 +1054,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1046,10 +1068,10 @@
     </row>
     <row r="9" spans="1:9" ht="15.6">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1061,7 +1083,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1075,10 +1097,10 @@
     </row>
     <row r="10" spans="1:9" ht="15.6">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1090,7 +1112,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1104,11 +1126,11 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
       <c r="C11">
         <v>0</v>
       </c>
@@ -1119,7 +1141,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1133,11 +1155,11 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
       <c r="C12">
         <v>1</v>
       </c>
@@ -1148,7 +1170,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1162,10 +1184,10 @@
     </row>
     <row r="13" spans="1:9" ht="15.6">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1177,7 +1199,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1191,11 +1213,11 @@
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
         <v>16</v>
       </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
       <c r="C14">
         <v>1</v>
       </c>
@@ -1206,7 +1228,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1220,10 +1242,10 @@
     </row>
     <row r="15" spans="1:9" ht="15.6">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1235,7 +1257,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1249,10 +1271,10 @@
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
         <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1264,7 +1286,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1278,10 +1300,10 @@
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
         <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1293,7 +1315,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1307,10 +1329,10 @@
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
         <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1322,7 +1344,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1336,10 +1358,10 @@
     </row>
     <row r="19" spans="1:9" ht="15.6">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1351,7 +1373,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1365,10 +1387,10 @@
     </row>
     <row r="20" spans="1:9" ht="15.6">
       <c r="A20" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1380,7 +1402,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1394,10 +1416,10 @@
     </row>
     <row r="21" spans="1:9" ht="15.6">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1409,7 +1431,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1423,10 +1445,10 @@
     </row>
     <row r="22" spans="1:9" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1438,7 +1460,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1452,10 +1474,10 @@
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
         <v>28</v>
-      </c>
-      <c r="B23" t="s">
-        <v>29</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1467,7 +1489,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1481,10 +1503,10 @@
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
         <v>30</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -1496,7 +1518,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1508,12 +1530,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15">
+    <row r="25" spans="1:9" ht="15.6">
       <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1525,7 +1547,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1539,10 +1561,10 @@
     </row>
     <row r="26" spans="1:9" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1554,7 +1576,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1568,10 +1590,10 @@
     </row>
     <row r="27" spans="1:9" ht="15.6">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1583,7 +1605,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1597,10 +1619,10 @@
     </row>
     <row r="28" spans="1:9" ht="15.6">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1612,7 +1634,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1626,10 +1648,10 @@
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1641,7 +1663,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1655,10 +1677,10 @@
     </row>
     <row r="30" spans="1:9" ht="15.6">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1670,7 +1692,7 @@
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1684,10 +1706,10 @@
     </row>
     <row r="31" spans="1:9" ht="15.6">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1699,7 +1721,7 @@
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1713,10 +1735,10 @@
     </row>
     <row r="32" spans="1:9" ht="15.6">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1728,7 +1750,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1742,10 +1764,10 @@
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1757,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1771,10 +1793,10 @@
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1786,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1795,15 +1817,15 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1815,7 +1837,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1829,10 +1851,10 @@
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1844,7 +1866,7 @@
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -1858,10 +1880,10 @@
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1873,7 +1895,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1887,10 +1909,10 @@
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1902,7 +1924,7 @@
         <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -1916,10 +1938,10 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1931,7 +1953,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -1940,15 +1962,15 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1960,7 +1982,7 @@
         <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -1974,10 +1996,10 @@
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1989,7 +2011,7 @@
         <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2001,12 +2023,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15">
+    <row r="42" spans="1:9" ht="15.6">
       <c r="A42" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2018,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2032,10 +2054,10 @@
     </row>
     <row r="43" spans="1:9" ht="15.6">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2047,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2056,15 +2078,15 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2076,7 +2098,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2088,15 +2110,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15">
+    <row r="45" spans="1:9" ht="15.6">
       <c r="A45" t="s">
-        <v>64</v>
-      </c>
-      <c r="B45" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2105,7 +2127,7 @@
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -2117,12 +2139,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15">
+    <row r="46" spans="1:9" ht="15.6">
       <c r="A46" t="s">
-        <v>66</v>
-      </c>
-      <c r="B46" t="s">
-        <v>67</v>
+        <v>62</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2134,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -2148,13 +2170,13 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2163,7 +2185,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -2175,12 +2197,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15">
+    <row r="48" spans="1:9" ht="15.6">
       <c r="A48" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -2192,7 +2214,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -2204,27 +2226,85 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="3:9">
+    <row r="49" spans="1:9" ht="15.6">
+      <c r="A49" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15.6">
+      <c r="A50" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>6</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="C51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/New/Magic.xlsx
+++ b/Assets/Resource/Magic/New/Magic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity_Project\Unity_Card\Assets\Resource\Magic\New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Unity_Card\Unity_Card\Assets\Resource\Magic\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC7E052-3D73-4136-81FA-6083F67B7FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DC8F91-960F-45B0-8D91-078A57AD338C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -201,256 +201,283 @@
     <t>巫术响指</t>
   </si>
   <si>
+    <t>城墙术</t>
+  </si>
+  <si>
+    <t>风暴</t>
+  </si>
+  <si>
+    <t>扭曲空间</t>
+  </si>
+  <si>
+    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
+  </si>
+  <si>
+    <t>杀戮本能</t>
+  </si>
+  <si>
+    <t>铸剑</t>
+  </si>
+  <si>
+    <t>魔典</t>
+  </si>
+  <si>
+    <t>权杖</t>
+  </si>
+  <si>
+    <t>恢复两点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kindDescription</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timingForPutting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Property</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理防御</t>
+  </si>
+  <si>
+    <t>物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击/物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以将一张法术牌转化为法力牌微光（恢复一点法力）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点水元素伤害\n防御时抵挡一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，草法术额外附带摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复一点法力，摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烧伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你使用火法术防御时，对方损失一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以将任意两张牌转化为一个圆盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术和草系技能可以转化为圆盾使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤蔓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荆棘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加三点法力上限（不增加法力值），恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵挡一点任意类型伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵挡一点任意类型伤害，可以将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一种元素，风暴转化为该元素法术。造成等同于当前法力值的伤害，并且消耗所有法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击使你的死亡感应触发时，你摸一张牌并且恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你的攻击触发对方的死亡感应后，你摸一张牌并且恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用元素法术时，可以选择额外消耗两点法力，额外附带两点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺客护符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的物理攻击只能被 物理防御或者抵挡任意属性伤害的防御 挡住</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻结束时恢复一点法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
-  </si>
-  <si>
-    <t>城墙术</t>
-  </si>
-  <si>
-    <t>风暴</t>
-  </si>
-  <si>
-    <t>扭曲空间</t>
-  </si>
-  <si>
-    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
-  </si>
-  <si>
-    <t>杀戮本能</t>
-  </si>
-  <si>
-    <t>铸剑</t>
-  </si>
-  <si>
-    <t>魔典</t>
-  </si>
-  <si>
-    <t>可以将物理攻击牌转化为特殊法术机遇（0消耗，摸一张牌）</t>
-  </si>
-  <si>
-    <t>权杖</t>
-  </si>
-  <si>
-    <t>恢复两点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kindDescription</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isSkill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>timingForPutting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Property</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effectCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理防御</t>
-  </si>
-  <si>
-    <t>物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击/物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻开始时恢复一点法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，可以将一张法术牌转化为法力牌微光（恢复一点法力）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点水元素伤害\n防御时抵挡一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，草法术额外附带摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复一点法力，摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>烧伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你使用火法术防御时，对方损失一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你可以将任意两张牌转化为一个圆盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草法术和草系技能可以转化为圆盾使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藤蔓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>荆棘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加三点法力上限（不增加法力值），恢复一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵挡一点任意类型伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵挡一点任意类型伤害，可以将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择一种元素，风暴转化为该元素法术。造成等同于当前法力值的伤害，并且消耗所有法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到攻击使你的死亡感应触发时，你摸一张牌并且恢复一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你的攻击触发对方的死亡感应后，你摸一张牌并且恢复一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，可以消耗一法力，将你本回合使用的所有（非转化的）剑刺全部收回手中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用元素法术时，可以选择额外消耗两点法力，额外附带两点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刺客护符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的物理攻击只能被 物理防御或者抵挡任意属性伤害的防御 挡住</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以将一张物理攻击/两张物理防御转化为一张特殊法术机遇（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>消耗，摸一张牌）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以消耗一法力，将你本回合使用的所有（非转化的）物理攻击全部收回手中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,7 +485,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -486,6 +513,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -507,11 +540,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -851,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G1">
         <v>2</v>
@@ -868,7 +902,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -880,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -909,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -938,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -955,7 +989,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -967,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -981,10 +1015,10 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -996,7 +1030,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1010,10 +1044,10 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1025,7 +1059,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1039,10 +1073,10 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1054,7 +1088,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1071,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1083,7 +1117,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1100,7 +1134,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1112,7 +1146,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1141,7 +1175,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1170,7 +1204,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1187,7 +1221,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1199,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1228,7 +1262,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1245,7 +1279,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1257,7 +1291,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1286,7 +1320,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1315,7 +1349,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1344,7 +1378,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1361,7 +1395,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1373,7 +1407,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1387,10 +1421,10 @@
     </row>
     <row r="20" spans="1:9" ht="15.6">
       <c r="A20" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1402,7 +1436,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1419,7 +1453,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1431,7 +1465,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1445,7 +1479,7 @@
     </row>
     <row r="22" spans="1:9" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
@@ -1460,7 +1494,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1489,7 +1523,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1518,7 +1552,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1535,7 +1569,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1547,7 +1581,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1561,10 +1595,10 @@
     </row>
     <row r="26" spans="1:9" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1576,7 +1610,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1593,7 +1627,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1605,7 +1639,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1622,7 +1656,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1634,7 +1668,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1663,7 +1697,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1680,7 +1714,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1692,7 +1726,7 @@
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1709,7 +1743,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1721,7 +1755,7 @@
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1738,7 +1772,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1750,7 +1784,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1779,7 +1813,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1808,7 +1842,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1837,7 +1871,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1866,7 +1900,7 @@
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -1895,7 +1929,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1924,7 +1958,7 @@
         <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -1953,7 +1987,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -1962,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
@@ -1982,7 +2016,7 @@
         <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -1994,12 +2028,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15">
+    <row r="41" spans="1:9" ht="15.6">
       <c r="A41" t="s">
         <v>55</v>
       </c>
-      <c r="B41" t="s">
-        <v>56</v>
+      <c r="B41" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -2011,7 +2045,7 @@
         <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2025,10 +2059,10 @@
     </row>
     <row r="42" spans="1:9" ht="15.6">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2040,7 +2074,7 @@
         <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2054,10 +2088,10 @@
     </row>
     <row r="43" spans="1:9" ht="15.6">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2069,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2078,15 +2112,15 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
         <v>59</v>
-      </c>
-      <c r="B44" t="s">
-        <v>60</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2098,7 +2132,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2112,10 +2146,10 @@
     </row>
     <row r="45" spans="1:9" ht="15.6">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -2127,7 +2161,7 @@
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -2141,10 +2175,10 @@
     </row>
     <row r="46" spans="1:9" ht="15.6">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2156,7 +2190,7 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -2168,12 +2202,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15">
+    <row r="47" spans="1:9" ht="15.6">
       <c r="A47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2185,7 +2219,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -2199,10 +2233,10 @@
     </row>
     <row r="48" spans="1:9" ht="15.6">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -2214,7 +2248,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -2228,10 +2262,10 @@
     </row>
     <row r="49" spans="1:9" ht="15.6">
       <c r="A49" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2243,7 +2277,7 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2257,10 +2291,10 @@
     </row>
     <row r="50" spans="1:9" ht="15.6">
       <c r="A50" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -2272,7 +2306,7 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -2286,25 +2320,25 @@
     </row>
     <row r="51" spans="1:9">
       <c r="C51" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="G51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="I51" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/New/Magic.xlsx
+++ b/Assets/Resource/Magic/New/Magic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Unity_Card\Unity_Card\Assets\Resource\Magic\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DC8F91-960F-45B0-8D91-078A57AD338C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEF8B70-31C3-4004-9F2F-AB1AA59A3148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,9 +117,6 @@
     <t>狂躁蘑菇</t>
   </si>
   <si>
-    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（0消耗，摸一张牌）</t>
-  </si>
-  <si>
     <t>木盾</t>
   </si>
   <si>
@@ -165,9 +162,6 @@
     <t>电弧</t>
   </si>
   <si>
-    <t>每使用一张物理攻击，恢复一点法力</t>
-  </si>
-  <si>
     <t>龟甲</t>
   </si>
   <si>
@@ -356,10 +350,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>进攻时，可以将一张法术牌转化为法力牌微光（恢复一点法力）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>进攻时造成一点水元素伤害\n防御时抵挡一点火元素伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -432,14 +422,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>刺客护符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的物理攻击只能被 物理防御或者抵挡任意属性伤害的防御 挡住</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>进攻结束时恢复一点法力值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -448,36 +430,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可以将一张物理攻击/两张物理防御转化为一张特殊法术机遇（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>消耗，摸一张牌）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，可以消耗一法力，将你本回合使用的所有（非转化的）物理攻击全部收回手中</t>
+    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（效果为摸一张牌）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以将一张法术牌转化为法力牌微光（效果为恢复一点法力）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将一张物理攻击/两张物理防御转化为一张特殊法术机遇（效果为摸一张牌）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立即恢复一点法力。每使用一张物理攻击，恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以将此卡牌翻面，视为你使用了一张剑刺。可以消耗一点法力值，使其恢复正面向上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑刃护符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当对方的死亡感应触发后，你的物理攻击不消耗法力值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,7 +462,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -513,12 +490,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -540,12 +511,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -885,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G1">
         <v>2</v>
@@ -902,7 +872,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -914,7 +884,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -943,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -972,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -989,7 +959,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1001,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -1015,10 +985,10 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1030,7 +1000,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1044,10 +1014,10 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1059,7 +1029,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1073,10 +1043,10 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1088,7 +1058,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1105,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1117,7 +1087,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1134,7 +1104,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1146,7 +1116,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1175,7 +1145,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1204,7 +1174,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1221,7 +1191,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1233,7 +1203,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1262,7 +1232,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1279,7 +1249,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1291,7 +1261,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1320,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1349,7 +1319,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1378,7 +1348,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1395,7 +1365,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1407,7 +1377,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1421,10 +1391,10 @@
     </row>
     <row r="20" spans="1:9" ht="15.6">
       <c r="A20" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1436,7 +1406,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1453,7 +1423,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1465,7 +1435,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1479,7 +1449,7 @@
     </row>
     <row r="22" spans="1:9" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
@@ -1494,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1506,12 +1476,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15">
+    <row r="23" spans="1:9" ht="15.6">
       <c r="A23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" t="s">
-        <v>28</v>
+      <c r="B23" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1523,7 +1493,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1537,10 +1507,10 @@
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
         <v>29</v>
-      </c>
-      <c r="B24" t="s">
-        <v>30</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -1552,7 +1522,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1566,10 +1536,10 @@
     </row>
     <row r="25" spans="1:9" ht="15.6">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1581,7 +1551,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1595,10 +1565,10 @@
     </row>
     <row r="26" spans="1:9" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1610,7 +1580,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1624,10 +1594,10 @@
     </row>
     <row r="27" spans="1:9" ht="15.6">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1639,7 +1609,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1653,10 +1623,10 @@
     </row>
     <row r="28" spans="1:9" ht="15.6">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1668,7 +1638,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1682,10 +1652,10 @@
     </row>
     <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
         <v>34</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1697,7 +1667,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1711,10 +1681,10 @@
     </row>
     <row r="30" spans="1:9" ht="15.6">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1726,7 +1696,7 @@
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1740,10 +1710,10 @@
     </row>
     <row r="31" spans="1:9" ht="15.6">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1755,7 +1725,7 @@
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1769,10 +1739,10 @@
     </row>
     <row r="32" spans="1:9" ht="15.6">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1784,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1798,10 +1768,10 @@
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
         <v>39</v>
-      </c>
-      <c r="B33" t="s">
-        <v>40</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1813,7 +1783,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1827,10 +1797,10 @@
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
         <v>41</v>
-      </c>
-      <c r="B34" t="s">
-        <v>42</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1842,7 +1812,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1854,12 +1824,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15">
+    <row r="35" spans="1:9" ht="15.6">
       <c r="A35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1871,7 +1841,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1885,10 +1855,10 @@
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1900,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -1914,10 +1884,10 @@
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1929,7 +1899,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1943,10 +1913,10 @@
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1958,7 +1928,7 @@
         <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -1972,10 +1942,10 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1987,7 +1957,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -1996,15 +1966,15 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -2016,7 +1986,7 @@
         <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -2030,10 +2000,10 @@
     </row>
     <row r="41" spans="1:9" ht="15.6">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -2045,7 +2015,7 @@
         <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2059,10 +2029,10 @@
     </row>
     <row r="42" spans="1:9" ht="15.6">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2074,7 +2044,7 @@
         <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2088,10 +2058,10 @@
     </row>
     <row r="43" spans="1:9" ht="15.6">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2103,7 +2073,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2112,15 +2082,15 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2132,7 +2102,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2146,10 +2116,10 @@
     </row>
     <row r="45" spans="1:9" ht="15.6">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -2161,7 +2131,7 @@
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -2175,10 +2145,10 @@
     </row>
     <row r="46" spans="1:9" ht="15.6">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2190,7 +2160,7 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -2204,10 +2174,10 @@
     </row>
     <row r="47" spans="1:9" ht="15.6">
       <c r="A47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>120</v>
+        <v>60</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2219,7 +2189,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -2233,10 +2203,10 @@
     </row>
     <row r="48" spans="1:9" ht="15.6">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -2248,7 +2218,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -2262,10 +2232,10 @@
     </row>
     <row r="49" spans="1:9" ht="15.6">
       <c r="A49" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2277,7 +2247,7 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2291,22 +2261,22 @@
     </row>
     <row r="50" spans="1:9" ht="15.6">
       <c r="A50" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -2315,30 +2285,30 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="C51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="G51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="I51" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/New/Magic.xlsx
+++ b/Assets/Resource/Magic/New/Magic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Unity_Card\Unity_Card\Assets\Resource\Magic\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEF8B70-31C3-4004-9F2F-AB1AA59A3148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4F1248-E0B0-4FF0-B823-4A27E64644A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="124">
   <si>
     <t>剑刺</t>
   </si>
@@ -455,6 +455,14 @@
   </si>
   <si>
     <t>当对方的死亡感应触发后，你的物理攻击不消耗法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陀螺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你的手牌数少于两张时，立即摸牌补至两张</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -830,12 +838,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
     <col min="2" max="2" width="95.88671875" customWidth="1"/>
     <col min="6" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15">
@@ -2288,26 +2297,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
-      <c r="C51" s="2" t="s">
+    <row r="51" spans="1:9" ht="15.6">
+      <c r="A51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="C52" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G52" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H52" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I52" s="2" t="s">
         <v>69</v>
       </c>
     </row>

--- a/Assets/Resource/Magic/New/Magic.xlsx
+++ b/Assets/Resource/Magic/New/Magic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Unity_Card\Unity_Card\Assets\Resource\Magic\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4F1248-E0B0-4FF0-B823-4A27E64644A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94038B67-52A7-49E7-9F98-A95C2BCFC713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="130">
   <si>
     <t>剑刺</t>
   </si>
@@ -78,12 +78,6 @@
     <t>沼泽</t>
   </si>
   <si>
-    <t>水墙</t>
-  </si>
-  <si>
-    <t>水法术可以防御一次任意点的任意类型伤害</t>
-  </si>
-  <si>
     <t>蒸汽锅炉</t>
   </si>
   <si>
@@ -96,373 +90,419 @@
     <t>淬火</t>
   </si>
   <si>
+    <t>火雨</t>
+  </si>
+  <si>
+    <t>熔岩之甲</t>
+  </si>
+  <si>
+    <t>蒸腾</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>木盾</t>
+  </si>
+  <si>
+    <t>防御时可以将该技能翻面，视为你使用了一个圆盾。轮到你进攻时，此技能恢复正面</t>
+  </si>
+  <si>
+    <t>进化</t>
+  </si>
+  <si>
+    <t>光芒</t>
+  </si>
+  <si>
+    <t>凝露</t>
+  </si>
+  <si>
+    <t>辉光</t>
+  </si>
+  <si>
+    <t>恢复满法力值</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>图腾</t>
+  </si>
+  <si>
+    <t>结晶</t>
+  </si>
+  <si>
+    <t>透镜</t>
+  </si>
+  <si>
+    <t>法力牌额外恢复一点法力值</t>
+  </si>
+  <si>
+    <t>满月</t>
+  </si>
+  <si>
+    <t>当法力值大于等于2时，对于法术伤害，可以减少一点法力值，抵挡一点伤害</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>龟甲</t>
+  </si>
+  <si>
+    <t>使用元素法术防御时不消耗法力</t>
+  </si>
+  <si>
+    <t>启示</t>
+  </si>
+  <si>
+    <t>所有法术不再消耗法力，但无法再打出法力牌。因其它技能所导致的额外法力消耗不会减免</t>
+  </si>
+  <si>
+    <t>驱散</t>
+  </si>
+  <si>
+    <t>移除对方的1个技能</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>展示你的一张手牌，然后将模仿当做这张手牌立即使用。不可以模仿技能</t>
+  </si>
+  <si>
+    <t>坟场</t>
+  </si>
+  <si>
+    <t>获得对方刚使用完毕或者弃掉的一张手牌，不可以获得技能</t>
+  </si>
+  <si>
+    <t>巫术响指</t>
+  </si>
+  <si>
+    <t>城墙术</t>
+  </si>
+  <si>
+    <t>风暴</t>
+  </si>
+  <si>
+    <t>扭曲空间</t>
+  </si>
+  <si>
+    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
+  </si>
+  <si>
+    <t>杀戮本能</t>
+  </si>
+  <si>
+    <t>铸剑</t>
+  </si>
+  <si>
+    <t>魔典</t>
+  </si>
+  <si>
+    <t>权杖</t>
+  </si>
+  <si>
+    <t>恢复两点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kindDescription</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timingForPutting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Property</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理防御</t>
+  </si>
+  <si>
+    <t>物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击/物理防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草元素技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术额外附带摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时造成一点水元素伤害\n防御时抵挡一点火元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，草法术额外附带摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复一点法力，摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烧伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你使用火法术防御时，对方损失一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以将任意两张牌转化为一个圆盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草法术和草系技能可以转化为圆盾使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤蔓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荆棘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加三点法力上限（不增加法力值），恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵挡一点任意类型伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵挡一点任意类型伤害，可以将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击使你的死亡感应触发时，你摸一张牌并且恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你的攻击触发对方的死亡感应后，你摸一张牌并且恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用元素法术时，可以选择额外消耗两点法力，额外附带两点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻结束时恢复一点法力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，可以将一张法术牌转化为法力牌微光（效果为恢复一点法力）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将一张物理攻击/两张物理防御转化为一张特殊法术机遇（效果为摸一张牌）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立即恢复一点法力。每使用一张物理攻击，恢复一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陀螺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你没有手牌时，立即摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御时可以将该技能翻面，然后弃一张牌来阻挡一次伤害。轮到你进攻时，此技能将会恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>进攻时，物理攻击额外附带一点火元素伤害</t>
-  </si>
-  <si>
-    <t>火雨</t>
-  </si>
-  <si>
-    <t>使用火法术防御之后，本回合免疫草元素伤害</t>
-  </si>
-  <si>
-    <t>熔岩之甲</t>
-  </si>
-  <si>
-    <t>蒸腾</t>
-  </si>
-  <si>
-    <t>进攻时，草法术可以转化剑刺，物理攻击可以转化为火法术</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>木盾</t>
-  </si>
-  <si>
-    <t>防御时可以将该技能翻面，视为你使用了一个圆盾。轮到你进攻时，此技能恢复正面</t>
-  </si>
-  <si>
-    <t>进化</t>
-  </si>
-  <si>
-    <t>光芒</t>
-  </si>
-  <si>
-    <t>凝露</t>
-  </si>
-  <si>
-    <t>辉光</t>
-  </si>
-  <si>
-    <t>恢复满法力值</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>图腾</t>
-  </si>
-  <si>
-    <t>结晶</t>
-  </si>
-  <si>
-    <t>透镜</t>
-  </si>
-  <si>
-    <t>法力牌额外恢复一点法力值</t>
-  </si>
-  <si>
-    <t>满月</t>
-  </si>
-  <si>
-    <t>当法力值大于等于2时，对于法术伤害，可以减少一点法力值，抵挡一点伤害</t>
-  </si>
-  <si>
-    <t>电弧</t>
-  </si>
-  <si>
-    <t>龟甲</t>
-  </si>
-  <si>
-    <t>使用元素法术防御时不消耗法力</t>
-  </si>
-  <si>
-    <t>启示</t>
-  </si>
-  <si>
-    <t>所有法术不再消耗法力，但无法再打出法力牌。因其它技能所导致的额外法力消耗不会减免</t>
-  </si>
-  <si>
-    <t>驱散</t>
-  </si>
-  <si>
-    <t>移除对方的1个技能</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>展示你的一张手牌，然后将模仿当做这张手牌立即使用。不可以模仿技能</t>
-  </si>
-  <si>
-    <t>坟场</t>
-  </si>
-  <si>
-    <t>获得对方刚使用完毕或者弃掉的一张手牌，不可以获得技能</t>
-  </si>
-  <si>
-    <t>巫术响指</t>
-  </si>
-  <si>
-    <t>城墙术</t>
-  </si>
-  <si>
-    <t>风暴</t>
-  </si>
-  <si>
-    <t>扭曲空间</t>
-  </si>
-  <si>
-    <t>进攻时，你可以将手牌储存到技能上，也可以将储存的牌取出，最多储存两张牌（技能消失时牌也会消失）</t>
-  </si>
-  <si>
-    <t>杀戮本能</t>
-  </si>
-  <si>
-    <t>铸剑</t>
-  </si>
-  <si>
-    <t>魔典</t>
-  </si>
-  <si>
-    <t>权杖</t>
-  </si>
-  <si>
-    <t>恢复两点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kindDescription</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isSkill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>timingForPutting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Property</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effectCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理防御</t>
-  </si>
-  <si>
-    <t>物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理攻击/物理防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点物理伤害，或者防御时抵挡一点任意类型的伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草元素技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即将死亡时，复活并且恢复死亡感应，然后移除此技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术额外附带摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，水法术可以转化为草法术，草法术可以转化为火法术</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点火元素伤害\n防御时抵挡一点物理/草元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点草元素伤害\n防御时抵挡一点物理/水元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时造成一点水元素伤害\n防御时抵挡一点火元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，草法术额外附带摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复一点法力，摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>烧伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你使用火法术防御时，对方损失一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你可以将任意两张牌转化为一个圆盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>草法术和草系技能可以转化为圆盾使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藤蔓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>荆棘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加三点法力上限（不增加法力值），恢复一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵挡一点任意类型伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵挡一点任意类型伤害，可以将你的任意张牌替换成弃牌堆当中的圆盾（若有）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择一种元素，风暴转化为该元素法术。造成等同于当前法力值的伤害，并且消耗所有法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到攻击使你的死亡感应触发时，你摸一张牌并且恢复一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你的攻击触发对方的死亡感应后，你摸一张牌并且恢复一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用元素法术时，可以选择额外消耗两点法力，额外附带两点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻结束时恢复一点法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打断对方的一张法术牌，使此法术不能产生任何效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，物理防御可以转化草法术，草法术可以转化为特殊法术机遇（效果为摸一张牌）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，可以将一张法术牌转化为法力牌微光（效果为恢复一点法力）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以将一张物理攻击/两张物理防御转化为一张特殊法术机遇（效果为摸一张牌）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>立即恢复一点法力。每使用一张物理攻击，恢复一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，可以将此卡牌翻面，视为你使用了一张剑刺。可以消耗一点法力值，使其恢复正面向上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剑刃护符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当对方的死亡感应触发后，你的物理攻击不消耗法力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陀螺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你的手牌数少于两张时，立即摸牌补至两张</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星辰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>声明一种元素类型，风暴转化为该元素法术。造成 等同于当前法力值 的伤害，并且消耗所有法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，草法术可以转化为剑刺，物理攻击可以转化为火法术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，物理防御可以转化为草法术，草法术可以转化为特殊法术机遇（效果为摸一张牌）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡牌可以无限转化（转化过的牌还可以再转化）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，所有法术牌都可以转化为剑刺使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你在出牌阶段直接空过（不出牌、重铸、变更技能），则恢复两点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>免疫草元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>充能</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复一点法力，防御时可以抵挡一点法术伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复一点法力，本回合的下一张物理攻击牌，额外增加一点物理伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -838,7 +878,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I52"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -864,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G1">
         <v>2</v>
@@ -881,7 +922,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -893,7 +934,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -922,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -951,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -968,7 +1009,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -980,7 +1021,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -994,10 +1035,10 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1009,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1023,10 +1064,10 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1038,7 +1079,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1052,10 +1093,10 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1067,7 +1108,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1084,7 +1125,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1096,7 +1137,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1113,7 +1154,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1125,7 +1166,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1154,7 +1195,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1183,7 +1224,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1200,7 +1241,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1212,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1224,12 +1265,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
+    <row r="14" spans="1:9" ht="15.6">
+      <c r="A14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1241,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1255,10 +1296,10 @@
     </row>
     <row r="15" spans="1:9" ht="15.6">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1270,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1284,10 +1325,10 @@
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1299,7 +1340,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1311,12 +1352,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15">
+    <row r="17" spans="1:9" ht="15.6">
       <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1328,7 +1369,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1340,12 +1381,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15">
+    <row r="18" spans="1:9" ht="15.6">
       <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1357,7 +1398,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1371,10 +1412,10 @@
     </row>
     <row r="19" spans="1:9" ht="15.6">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1386,7 +1427,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1400,10 +1441,10 @@
     </row>
     <row r="20" spans="1:9" ht="15.6">
       <c r="A20" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1415,7 +1456,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1429,10 +1470,10 @@
     </row>
     <row r="21" spans="1:9" ht="15.6">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1444,7 +1485,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1458,10 +1499,10 @@
     </row>
     <row r="22" spans="1:9" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
+        <v>98</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1473,7 +1514,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1487,10 +1528,10 @@
     </row>
     <row r="23" spans="1:9" ht="15.6">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1502,7 +1543,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1516,10 +1557,10 @@
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -1531,7 +1572,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1545,10 +1586,10 @@
     </row>
     <row r="25" spans="1:9" ht="15.6">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1560,7 +1601,7 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1574,10 +1615,10 @@
     </row>
     <row r="26" spans="1:9" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1589,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1603,10 +1644,10 @@
     </row>
     <row r="27" spans="1:9" ht="15.6">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1618,7 +1659,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1632,10 +1673,10 @@
     </row>
     <row r="28" spans="1:9" ht="15.6">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1647,7 +1688,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1659,27 +1700,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" t="s">
-        <v>34</v>
+    <row r="29" spans="1:9" ht="15.6">
+      <c r="A29" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1689,11 +1730,11 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6">
-      <c r="A30" t="s">
-        <v>35</v>
+      <c r="A30" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1705,27 +1746,27 @@
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.6">
+    <row r="31" spans="1:9" ht="15">
       <c r="A31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>116</v>
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1734,13 +1775,13 @@
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1748,10 +1789,10 @@
     </row>
     <row r="32" spans="1:9" ht="15.6">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1763,7 +1804,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1775,15 +1816,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15">
+    <row r="33" spans="1:9" ht="15.6">
       <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1792,7 +1833,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1801,18 +1842,18 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.6">
       <c r="A34" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1821,7 +1862,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1833,15 +1874,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.6">
+    <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>118</v>
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>34</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1850,7 +1891,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1859,18 +1900,18 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1879,7 +1920,7 @@
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -1891,15 +1932,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15">
+    <row r="37" spans="1:9" ht="15.6">
       <c r="A37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" t="s">
-        <v>46</v>
+        <v>37</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1908,7 +1949,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1917,44 +1958,44 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1963,27 +2004,27 @@
         <v>1</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15">
-      <c r="A40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.6">
+      <c r="A40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1992,27 +2033,27 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.6">
+    <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>114</v>
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -2024,10 +2065,10 @@
         <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2036,12 +2077,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.6">
+    <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>106</v>
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2053,24 +2094,24 @@
         <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15.6">
+      <c r="I42" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>55</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2082,27 +2123,27 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15">
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15.6">
       <c r="A44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B44" t="s">
-        <v>57</v>
+        <v>48</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2111,24 +2152,24 @@
         <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.6">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -2140,24 +2181,24 @@
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.6">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2169,24 +2210,24 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G46">
         <v>2</v>
       </c>
       <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15.6">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>60</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>117</v>
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>52</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2198,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -2212,10 +2253,10 @@
     </row>
     <row r="48" spans="1:9" ht="15.6">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -2227,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -2236,15 +2277,15 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.6">
-      <c r="A49" s="1" t="s">
-        <v>111</v>
+      <c r="A49" t="s">
+        <v>54</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2256,7 +2297,7 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2269,11 +2310,11 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.6">
-      <c r="A50" s="1" t="s">
-        <v>120</v>
+      <c r="A50" t="s">
+        <v>55</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -2282,10 +2323,10 @@
         <v>1</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -2298,14 +2339,14 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.6">
-      <c r="A51" s="1" t="s">
-        <v>122</v>
+      <c r="A51" t="s">
+        <v>56</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2314,7 +2355,7 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -2323,30 +2364,117 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="C52" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15.6">
+      <c r="A52" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15.6">
+      <c r="A53" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>6</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15.6">
+      <c r="A54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="C55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="F55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I55" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/New/Magic.xlsx
+++ b/Assets/Resource/Magic/New/Magic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Unity_Card\Unity_Card\Assets\Resource\Magic\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94038B67-52A7-49E7-9F98-A95C2BCFC713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFB25C3-8A2F-43FF-86C5-93D5C8121B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="134">
   <si>
     <t>剑刺</t>
   </si>
@@ -201,9 +201,6 @@
     <t>魔典</t>
   </si>
   <si>
-    <t>权杖</t>
-  </si>
-  <si>
     <t>恢复两点法力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -351,10 +348,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>当你使用火法术防御时，对方损失一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>你可以将任意两张牌转化为一个圆盾</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -391,10 +384,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>所有元素法术防御时改为抵挡一点任意类型的伤害，并且抵挡类型相同的法术时不消耗法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大爆炸</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -411,26 +400,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>进攻时，可以将一张法术牌转化为法力牌微光（效果为恢复一点法力）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以将一张物理攻击/两张物理防御转化为一张特殊法术机遇（效果为摸一张牌）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>立即恢复一点法力。每使用一张物理攻击，恢复一点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陀螺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你没有手牌时，立即摸一张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>防御时可以将该技能翻面，然后弃一张牌来阻挡一次伤害。轮到你进攻时，此技能将会恢复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -443,10 +412,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>星辰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>声明一种元素类型，风暴转化为该元素法术。造成 等同于当前法力值 的伤害，并且消耗所有法力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -459,50 +424,91 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>免疫草元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复一点法力，防御时可以抵挡一点法术伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复一点法力，本回合的下一张物理攻击牌，额外增加一点物理伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火炬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，每打出一张水法术，本回合打出的下一张牌不消耗法力（包含技能牌和技能额外消耗）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回旋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>幻化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>卡牌可以无限转化（转化过的牌还可以再转化）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进攻时，所有法术牌都可以转化为剑刺使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果你在出牌阶段直接空过（不出牌、重铸、变更技能），则恢复两点法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>免疫草元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法力护盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>充能</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复一点法力，防御时可以抵挡一点法术伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复一点法力，本回合的下一张物理攻击牌，额外增加一点物理伤害</t>
+    <t>进攻时，可以将草法术转化为特殊法术重塑（不消耗法力，丢弃两张手牌，然后摸两张）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾打击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将两张牌转化为一张特殊法术机遇（效果为摸一张牌）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每当你从牌堆摸到一张剑刺时，展示你摸到的剑刺，然后多摸一张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摸牌阶段时，可以将此技能翻面然后多摸一张。使用元素法术防御时，此技能恢复正面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，每打出一张物理攻击，获得一点临时护盾。在你回合开始时，临时护盾消失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长生护符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堡垒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每使用一张物理攻击，恢复一点法力。对方死亡感应触发之后，改为恢复2点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将两张元素法术牌转化为一张法力牌强光（效果为恢复三点法力）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的物理防御牌可以转化为物理攻击牌盾击（效果为造成一点物理伤害，获得一点临时护盾）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你使用火法术防御时，你不会消耗法力，并且对方损失一点法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进攻时，每打出一张火法术，可以将弃牌堆中的一张牌（金卡和技能除外）移到摸牌堆顶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>充能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -879,11 +885,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="95.88671875" customWidth="1"/>
+    <col min="2" max="2" width="90.6640625" customWidth="1"/>
     <col min="6" max="6" width="16.88671875" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" customWidth="1"/>
   </cols>
@@ -905,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G1">
         <v>2</v>
@@ -922,7 +928,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -934,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -963,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -992,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1009,7 +1015,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1021,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -1035,10 +1041,10 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1050,7 +1056,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1064,10 +1070,10 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1079,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1093,10 +1099,10 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1108,7 +1114,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1125,7 +1131,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1137,7 +1143,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1154,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1166,7 +1172,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1195,7 +1201,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1207,73 +1213,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15">
-      <c r="A12" t="s">
+    <row r="12" spans="1:9" ht="15.6">
+      <c r="A12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.6">
-      <c r="A13" t="s">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.6">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="B14" s="1" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1282,7 +1288,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1291,44 +1297,44 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.6">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.6">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
+      <c r="B16" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1340,7 +1346,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1352,12 +1358,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6">
+    <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>116</v>
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1369,7 +1375,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1383,22 +1389,22 @@
     </row>
     <row r="18" spans="1:9" ht="15.6">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1411,11 +1417,11 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.6">
-      <c r="A19" t="s">
-        <v>20</v>
+      <c r="A19" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1427,7 +1433,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1436,15 +1442,15 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.6">
-      <c r="A20" s="1" t="s">
-        <v>93</v>
+      <c r="A20" t="s">
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1456,7 +1462,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1470,22 +1476,22 @@
     </row>
     <row r="21" spans="1:9" ht="15.6">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1499,22 +1505,22 @@
     </row>
     <row r="22" spans="1:9" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1528,10 +1534,10 @@
     </row>
     <row r="23" spans="1:9" ht="15.6">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1543,7 +1549,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1555,24 +1561,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
+    <row r="24" spans="1:9" ht="15.6">
+      <c r="A24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <v>4</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1581,27 +1587,27 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.6">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1615,13 +1621,13 @@
     </row>
     <row r="26" spans="1:9" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1630,7 +1636,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1642,59 +1648,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.6">
+    <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>92</v>
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.6">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1702,51 +1708,51 @@
     </row>
     <row r="29" spans="1:9" ht="15.6">
       <c r="A29" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6">
-      <c r="A30" s="2" t="s">
-        <v>127</v>
+      <c r="A30" t="s">
+        <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E30">
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1758,24 +1764,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15">
+    <row r="31" spans="1:9" ht="15.6">
       <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1788,40 +1794,40 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6">
-      <c r="A32" t="s">
-        <v>30</v>
+      <c r="A32" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.6">
-      <c r="A33" t="s">
-        <v>31</v>
+      <c r="A33" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1833,27 +1839,27 @@
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G33">
         <v>2</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.6">
+    <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>99</v>
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1862,27 +1868,27 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G34">
         <v>2</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15">
+    <row r="35" spans="1:9" ht="15.6">
       <c r="A35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1891,7 +1897,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1900,18 +1906,18 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.6">
       <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1920,7 +1926,7 @@
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -1934,10 +1940,10 @@
     </row>
     <row r="37" spans="1:9" ht="15.6">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1949,7 +1955,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1963,13 +1969,13 @@
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1978,7 +1984,7 @@
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -1987,15 +1993,15 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -2007,7 +2013,7 @@
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2016,15 +2022,15 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.6">
-      <c r="A40" s="1" t="s">
-        <v>117</v>
+      <c r="A40" t="s">
+        <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -2036,7 +2042,7 @@
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2050,39 +2056,39 @@
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G41">
         <v>2</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2091,30 +2097,30 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>85</v>
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2123,24 +2129,24 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15.6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>108</v>
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>45</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -2152,24 +2158,24 @@
         <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.6">
+      <c r="I44" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>101</v>
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -2181,27 +2187,27 @@
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.6">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2210,27 +2216,27 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15">
+      <c r="I46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15.6">
       <c r="A47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2239,24 +2245,24 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.6">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -2268,24 +2274,24 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15.6">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>123</v>
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2297,7 +2303,7 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2311,13 +2317,13 @@
     </row>
     <row r="50" spans="1:9" ht="15.6">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2326,7 +2332,7 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -2340,10 +2346,10 @@
     </row>
     <row r="51" spans="1:9" ht="15.6">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -2355,7 +2361,7 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -2368,11 +2374,11 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.6">
-      <c r="A52" s="1" t="s">
-        <v>105</v>
+      <c r="A52" t="s">
+        <v>55</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2384,7 +2390,7 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G52">
         <v>2</v>
@@ -2398,10 +2404,10 @@
     </row>
     <row r="53" spans="1:9" ht="15.6">
       <c r="A53" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -2413,7 +2419,7 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2427,10 +2433,10 @@
     </row>
     <row r="54" spans="1:9" ht="15.6">
       <c r="A54" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -2442,7 +2448,7 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -2454,27 +2460,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
-      <c r="C55" s="2" t="s">
+    <row r="55" spans="1:9" ht="15.6">
+      <c r="A55" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15.6">
+      <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="C57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="G57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I57" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
